--- a/output/pdf_financials_xlsx/SPRK.xlsx
+++ b/output/pdf_financials_xlsx/SPRK.xlsx
@@ -1928,13 +1928,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>7.467213</v>
+        <v>8.809151</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>7.467213</v>
+        <v>10.640472</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>7.467213</v>
+        <v>11.59019</v>
       </c>
     </row>
     <row r="93">
@@ -2335,13 +2335,13 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0.1175</v>
+        <v>-0.773558</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>2.683739</v>
+        <v>2.522247</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>3.1731</v>
+        <v>2.605384</v>
       </c>
     </row>
     <row r="119">
@@ -3077,7 +3077,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -3391,7 +3395,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E24" s="5" t="n">
         <v>1.341938</v>
       </c>
@@ -3902,7 +3910,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E41" s="5" t="n">
         <v>-0.891058</v>
       </c>

--- a/output/pdf_financials_xlsx/SPRK.xlsx
+++ b/output/pdf_financials_xlsx/SPRK.xlsx
@@ -976,13 +976,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.016633</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.200587</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.000954</v>
       </c>
     </row>
     <row r="35">
@@ -1008,13 +1008,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.002947</v>
+        <v>0.01958</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.001328</v>
+        <v>0.201915</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.000519</v>
+        <v>0.001473</v>
       </c>
     </row>
     <row r="37">
@@ -1200,13 +1200,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.0254</v>
+        <v>0.008767</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.212058</v>
+        <v>0.011471</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.887105</v>
+        <v>0.886151</v>
       </c>
     </row>
     <row r="49">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/SPRK.xlsx
+++ b/output/pdf_financials_xlsx/SPRK.xlsx
@@ -2287,7 +2287,7 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>0.129716</v>
       </c>
       <c r="C115" s="3" t="n">
         <v>0</v>
@@ -4431,7 +4431,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E58" s="5" t="n">
         <v>0.129716</v>
       </c>
